--- a/main/StructureDefinition-bc-practitioner-role.xlsx
+++ b/main/StructureDefinition-bc-practitioner-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T21:39:06+00:00</t>
+    <t>2026-04-01T23:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3301,7 +3301,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>192</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>203</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>213</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>229</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>234</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>239</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>244</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>279</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>290</v>
       </c>
@@ -7635,12 +7635,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN53">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
